--- a/BWI/bestwine_output/bestwine_Ireland.xlsx
+++ b/BWI/bestwine_output/bestwine_Ireland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA438"/>
+  <dimension ref="A1:AA446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -47780,6 +47780,822 @@
       <c r="Z438" s="2" t="inlineStr"/>
       <c r="AA438" s="2" t="inlineStr"/>
     </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>Bubble Brothers Limited</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
+          <t>Bubble Brothers Limited</t>
+        </is>
+      </c>
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>26091</t>
+        </is>
+      </c>
+      <c r="D439" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E439" s="2" t="inlineStr">
+        <is>
+          <t>Cork</t>
+        </is>
+      </c>
+      <c r="F439" s="2" t="inlineStr">
+        <is>
+          <t>County Cork</t>
+        </is>
+      </c>
+      <c r="G439" s="2" t="inlineStr">
+        <is>
+          <t>Marina Commercial Park, Centre Park Road</t>
+        </is>
+      </c>
+      <c r="H439" s="2" t="inlineStr">
+        <is>
+          <t>T12 ND2W</t>
+        </is>
+      </c>
+      <c r="I439" s="2" t="inlineStr">
+        <is>
+          <t>http://www.marypawlewines.com, https://bubblebrothers.ie</t>
+        </is>
+      </c>
+      <c r="J439" s="2" t="inlineStr"/>
+      <c r="K439" s="2" t="inlineStr"/>
+      <c r="L439" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M439" s="2" t="inlineStr"/>
+      <c r="N439" s="2" t="inlineStr">
+        <is>
+          <t>info@bubblebrothers.ie</t>
+        </is>
+      </c>
+      <c r="O439" s="2" t="inlineStr">
+        <is>
+          <t>+353 21 431 6000</t>
+        </is>
+      </c>
+      <c r="P439" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q439" s="2" t="inlineStr">
+        <is>
+          <t>291250</t>
+        </is>
+      </c>
+      <c r="R439" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bubble-brothers</t>
+        </is>
+      </c>
+      <c r="S439" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bubblebrothers</t>
+        </is>
+      </c>
+      <c r="T439" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bubblebrotherscork/</t>
+        </is>
+      </c>
+      <c r="U439" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/bubblebrothers</t>
+        </is>
+      </c>
+      <c r="V439" s="2" t="inlineStr"/>
+      <c r="W439" s="2" t="inlineStr">
+        <is>
+          <t>Billy Forrester</t>
+        </is>
+      </c>
+      <c r="X439" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y439" s="2" t="inlineStr"/>
+      <c r="Z439" s="2" t="inlineStr"/>
+      <c r="AA439" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/billy-forrester-a5697b36/</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>Jj Mahons &amp; Sons</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="inlineStr">
+        <is>
+          <t>Jj Mahons &amp; Sons</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>20930</t>
+        </is>
+      </c>
+      <c r="D440" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>Kildare</t>
+        </is>
+      </c>
+      <c r="F440" s="2" t="inlineStr">
+        <is>
+          <t>County Kildare</t>
+        </is>
+      </c>
+      <c r="G440" s="2" t="inlineStr">
+        <is>
+          <t>Cross Keys</t>
+        </is>
+      </c>
+      <c r="H440" s="2" t="inlineStr">
+        <is>
+          <t>R51 C625</t>
+        </is>
+      </c>
+      <c r="I440" s="2" t="inlineStr">
+        <is>
+          <t>http://jjmahons.com</t>
+        </is>
+      </c>
+      <c r="J440" s="2" t="inlineStr"/>
+      <c r="K440" s="2" t="inlineStr"/>
+      <c r="L440" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M440" s="2" t="inlineStr"/>
+      <c r="N440" s="2" t="inlineStr">
+        <is>
+          <t>info@jjmahons.com</t>
+        </is>
+      </c>
+      <c r="O440" s="2" t="inlineStr">
+        <is>
+          <t>+353 45 521 316</t>
+        </is>
+      </c>
+      <c r="P440" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="Q440" s="2" t="inlineStr">
+        <is>
+          <t>32542</t>
+        </is>
+      </c>
+      <c r="R440" s="2" t="inlineStr"/>
+      <c r="S440" s="2" t="inlineStr"/>
+      <c r="T440" s="2" t="inlineStr"/>
+      <c r="U440" s="2" t="inlineStr"/>
+      <c r="V440" s="2" t="inlineStr"/>
+      <c r="W440" s="2" t="inlineStr">
+        <is>
+          <t>David Mahon</t>
+        </is>
+      </c>
+      <c r="X440" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y440" s="2" t="inlineStr"/>
+      <c r="Z440" s="2" t="inlineStr"/>
+      <c r="AA440" s="2" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>Jj Mahons &amp; Sons</t>
+        </is>
+      </c>
+      <c r="B441" s="2" t="inlineStr">
+        <is>
+          <t>Jj Mahons &amp; Sons</t>
+        </is>
+      </c>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>20930</t>
+        </is>
+      </c>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>Kildare</t>
+        </is>
+      </c>
+      <c r="F441" s="2" t="inlineStr">
+        <is>
+          <t>County Kildare</t>
+        </is>
+      </c>
+      <c r="G441" s="2" t="inlineStr">
+        <is>
+          <t>Cross Keys</t>
+        </is>
+      </c>
+      <c r="H441" s="2" t="inlineStr">
+        <is>
+          <t>R51 C625</t>
+        </is>
+      </c>
+      <c r="I441" s="2" t="inlineStr">
+        <is>
+          <t>http://jjmahons.com</t>
+        </is>
+      </c>
+      <c r="J441" s="2" t="inlineStr"/>
+      <c r="K441" s="2" t="inlineStr"/>
+      <c r="L441" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M441" s="2" t="inlineStr"/>
+      <c r="N441" s="2" t="inlineStr">
+        <is>
+          <t>info@jjmahons.com</t>
+        </is>
+      </c>
+      <c r="O441" s="2" t="inlineStr">
+        <is>
+          <t>+353 45 521 316</t>
+        </is>
+      </c>
+      <c r="P441" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="Q441" s="2" t="inlineStr">
+        <is>
+          <t>32542</t>
+        </is>
+      </c>
+      <c r="R441" s="2" t="inlineStr"/>
+      <c r="S441" s="2" t="inlineStr"/>
+      <c r="T441" s="2" t="inlineStr"/>
+      <c r="U441" s="2" t="inlineStr"/>
+      <c r="V441" s="2" t="inlineStr"/>
+      <c r="W441" s="2" t="inlineStr">
+        <is>
+          <t>Julie McMahon</t>
+        </is>
+      </c>
+      <c r="X441" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y441" s="2" t="inlineStr"/>
+      <c r="Z441" s="2" t="inlineStr"/>
+      <c r="AA441" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/julie-mcmahon-2595ab35/</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>Copsewood Limited</t>
+        </is>
+      </c>
+      <c r="B442" s="2" t="inlineStr">
+        <is>
+          <t>Copsewood Limited</t>
+        </is>
+      </c>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>8051</t>
+        </is>
+      </c>
+      <c r="D442" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F442" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>Portmarnock Town Centre,  Strand Road, Portmarnock</t>
+        </is>
+      </c>
+      <c r="H442" s="2" t="inlineStr">
+        <is>
+          <t>D13 FP28</t>
+        </is>
+      </c>
+      <c r="I442" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jusdevine.ie</t>
+        </is>
+      </c>
+      <c r="J442" s="2" t="inlineStr"/>
+      <c r="K442" s="2" t="inlineStr"/>
+      <c r="L442" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M442" s="2" t="inlineStr"/>
+      <c r="N442" s="2" t="inlineStr">
+        <is>
+          <t>info@jusdevine.ie</t>
+        </is>
+      </c>
+      <c r="O442" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 846 1192</t>
+        </is>
+      </c>
+      <c r="P442" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q442" s="2" t="inlineStr">
+        <is>
+          <t>167088</t>
+        </is>
+      </c>
+      <c r="R442" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jus-de-vine-wine-shop/</t>
+        </is>
+      </c>
+      <c r="S442" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/jusdevineportmarnock/</t>
+        </is>
+      </c>
+      <c r="T442" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jusdevine_/</t>
+        </is>
+      </c>
+      <c r="U442" s="2" t="inlineStr"/>
+      <c r="V442" s="2" t="inlineStr"/>
+      <c r="W442" s="2" t="inlineStr"/>
+      <c r="X442" s="2" t="inlineStr"/>
+      <c r="Y442" s="2" t="inlineStr"/>
+      <c r="Z442" s="2" t="inlineStr"/>
+      <c r="AA442" s="2" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>O'donovans Off Licence Limited</t>
+        </is>
+      </c>
+      <c r="B443" s="2" t="inlineStr">
+        <is>
+          <t>O'donovans Off Licence Limited</t>
+        </is>
+      </c>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>8071</t>
+        </is>
+      </c>
+      <c r="D443" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
+        <is>
+          <t>Cork</t>
+        </is>
+      </c>
+      <c r="F443" s="2" t="inlineStr">
+        <is>
+          <t>Co. Cork</t>
+        </is>
+      </c>
+      <c r="G443" s="2" t="inlineStr">
+        <is>
+          <t>Cork Bonded Warehouse, Little Island Business Park, Little Island</t>
+        </is>
+      </c>
+      <c r="H443" s="2" t="inlineStr">
+        <is>
+          <t>T45 VY26</t>
+        </is>
+      </c>
+      <c r="I443" s="2" t="inlineStr">
+        <is>
+          <t>https://www.odonovansofflicence.com</t>
+        </is>
+      </c>
+      <c r="J443" s="2" t="inlineStr"/>
+      <c r="K443" s="2" t="inlineStr"/>
+      <c r="L443" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M443" s="2" t="inlineStr"/>
+      <c r="N443" s="2" t="inlineStr">
+        <is>
+          <t>info@odonovansofflicence.com</t>
+        </is>
+      </c>
+      <c r="O443" s="2" t="inlineStr">
+        <is>
+          <t>+353 21 429 6060</t>
+        </is>
+      </c>
+      <c r="P443" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q443" s="2" t="inlineStr">
+        <is>
+          <t>331387</t>
+        </is>
+      </c>
+      <c r="R443" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/o'donovans-off-licence</t>
+        </is>
+      </c>
+      <c r="S443" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/odonovansofflicences</t>
+        </is>
+      </c>
+      <c r="T443" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/odonovansofflicence</t>
+        </is>
+      </c>
+      <c r="U443" s="2" t="inlineStr"/>
+      <c r="V443" s="2" t="inlineStr"/>
+      <c r="W443" s="2" t="inlineStr">
+        <is>
+          <t>Gary O'Donovan</t>
+        </is>
+      </c>
+      <c r="X443" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y443" s="2" t="inlineStr"/>
+      <c r="Z443" s="2" t="inlineStr"/>
+      <c r="AA443" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gary-o-donovan-ba-wset-dip-59a92616/</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>Tankersley Wine Brokers Limited</t>
+        </is>
+      </c>
+      <c r="B444" s="2" t="inlineStr">
+        <is>
+          <t>Tankersley Wine Brokers Limited</t>
+        </is>
+      </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>8023</t>
+        </is>
+      </c>
+      <c r="D444" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr">
+        <is>
+          <t>Tinahely</t>
+        </is>
+      </c>
+      <c r="F444" s="2" t="inlineStr">
+        <is>
+          <t>Co. Wicklow</t>
+        </is>
+      </c>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>Tankersley Cottage, Preban</t>
+        </is>
+      </c>
+      <c r="H444" s="2" t="inlineStr">
+        <is>
+          <t>Y14 YV09</t>
+        </is>
+      </c>
+      <c r="I444" s="2" t="inlineStr">
+        <is>
+          <t>https://tankersleywine.com</t>
+        </is>
+      </c>
+      <c r="J444" s="2" t="inlineStr"/>
+      <c r="K444" s="2" t="inlineStr"/>
+      <c r="L444" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M444" s="2" t="inlineStr"/>
+      <c r="N444" s="2" t="inlineStr">
+        <is>
+          <t>info@tankersleywine.ie</t>
+        </is>
+      </c>
+      <c r="O444" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 485 2694</t>
+        </is>
+      </c>
+      <c r="P444" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q444" s="2" t="inlineStr">
+        <is>
+          <t>329628</t>
+        </is>
+      </c>
+      <c r="R444" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tankersley-wine-brokers/</t>
+        </is>
+      </c>
+      <c r="S444" s="2" t="inlineStr"/>
+      <c r="T444" s="2" t="inlineStr"/>
+      <c r="U444" s="2" t="inlineStr"/>
+      <c r="V444" s="2" t="inlineStr"/>
+      <c r="W444" s="2" t="inlineStr"/>
+      <c r="X444" s="2" t="inlineStr"/>
+      <c r="Y444" s="2" t="inlineStr"/>
+      <c r="Z444" s="2" t="inlineStr"/>
+      <c r="AA444" s="2" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>J.j. Fox Limited</t>
+        </is>
+      </c>
+      <c r="B445" s="2" t="inlineStr">
+        <is>
+          <t>J.j. Fox Limited</t>
+        </is>
+      </c>
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>28785</t>
+        </is>
+      </c>
+      <c r="D445" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F445" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G445" s="2" t="inlineStr">
+        <is>
+          <t>119 Grafton Street</t>
+        </is>
+      </c>
+      <c r="H445" s="2" t="inlineStr">
+        <is>
+          <t>D02 E620</t>
+        </is>
+      </c>
+      <c r="I445" s="2" t="inlineStr">
+        <is>
+          <t>https://jamesfox.ie</t>
+        </is>
+      </c>
+      <c r="J445" s="2" t="inlineStr"/>
+      <c r="K445" s="2" t="inlineStr"/>
+      <c r="L445" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M445" s="2" t="inlineStr"/>
+      <c r="N445" s="2" t="inlineStr">
+        <is>
+          <t>info@jamesfox.ie</t>
+        </is>
+      </c>
+      <c r="O445" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 677 0533</t>
+        </is>
+      </c>
+      <c r="P445" s="2" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="Q445" s="2" t="inlineStr">
+        <is>
+          <t>9864</t>
+        </is>
+      </c>
+      <c r="R445" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/james-fox-cigar-&amp;-whiskey-store</t>
+        </is>
+      </c>
+      <c r="S445" s="2" t="inlineStr"/>
+      <c r="T445" s="2" t="inlineStr"/>
+      <c r="U445" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/jamesfoxdublin</t>
+        </is>
+      </c>
+      <c r="V445" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/JamesJFoxDublin</t>
+        </is>
+      </c>
+      <c r="W445" s="2" t="inlineStr">
+        <is>
+          <t>Yiorgos Manesis</t>
+        </is>
+      </c>
+      <c r="X445" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y445" s="2" t="inlineStr"/>
+      <c r="Z445" s="2" t="inlineStr"/>
+      <c r="AA445" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/yiorgosmanesis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>J.j. Fox Limited</t>
+        </is>
+      </c>
+      <c r="B446" s="2" t="inlineStr">
+        <is>
+          <t>J.j. Fox Limited</t>
+        </is>
+      </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>28785</t>
+        </is>
+      </c>
+      <c r="D446" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F446" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G446" s="2" t="inlineStr">
+        <is>
+          <t>119 Grafton Street</t>
+        </is>
+      </c>
+      <c r="H446" s="2" t="inlineStr">
+        <is>
+          <t>D02 E620</t>
+        </is>
+      </c>
+      <c r="I446" s="2" t="inlineStr">
+        <is>
+          <t>https://jamesfox.ie</t>
+        </is>
+      </c>
+      <c r="J446" s="2" t="inlineStr"/>
+      <c r="K446" s="2" t="inlineStr"/>
+      <c r="L446" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M446" s="2" t="inlineStr"/>
+      <c r="N446" s="2" t="inlineStr">
+        <is>
+          <t>info@jamesfox.ie</t>
+        </is>
+      </c>
+      <c r="O446" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 677 0533</t>
+        </is>
+      </c>
+      <c r="P446" s="2" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="Q446" s="2" t="inlineStr">
+        <is>
+          <t>9864</t>
+        </is>
+      </c>
+      <c r="R446" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/james-fox-cigar-&amp;-whiskey-store</t>
+        </is>
+      </c>
+      <c r="S446" s="2" t="inlineStr"/>
+      <c r="T446" s="2" t="inlineStr"/>
+      <c r="U446" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/jamesfoxdublin</t>
+        </is>
+      </c>
+      <c r="V446" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/JamesJFoxDublin</t>
+        </is>
+      </c>
+      <c r="W446" s="2" t="inlineStr">
+        <is>
+          <t>Amy Catherine</t>
+        </is>
+      </c>
+      <c r="X446" s="2" t="inlineStr">
+        <is>
+          <t>Sales Executive</t>
+        </is>
+      </c>
+      <c r="Y446" s="2" t="inlineStr"/>
+      <c r="Z446" s="2" t="inlineStr"/>
+      <c r="AA446" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/amy-catherine-mcloughlin-4246a819a/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Ireland.xlsx
+++ b/BWI/bestwine_output/bestwine_Ireland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA446"/>
+  <dimension ref="A1:AA456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -48596,6 +48596,1052 @@
         </is>
       </c>
     </row>
+    <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>Supervalu Ireland</t>
+        </is>
+      </c>
+      <c r="B447" s="2" t="inlineStr">
+        <is>
+          <t>Supervalu Ireland</t>
+        </is>
+      </c>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>108273</t>
+        </is>
+      </c>
+      <c r="D447" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 12</t>
+        </is>
+      </c>
+      <c r="F447" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G447" s="2" t="inlineStr">
+        <is>
+          <t>Walkinstown</t>
+        </is>
+      </c>
+      <c r="H447" s="2" t="inlineStr">
+        <is>
+          <t>D12 XDK2</t>
+        </is>
+      </c>
+      <c r="I447" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.supervalu.ie, https://supervalu.ie</t>
+        </is>
+      </c>
+      <c r="J447" s="2" t="inlineStr"/>
+      <c r="K447" s="2" t="inlineStr"/>
+      <c r="L447" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M447" s="2" t="inlineStr"/>
+      <c r="N447" s="2" t="inlineStr">
+        <is>
+          <t>hannonenfield@supervalu.ie</t>
+        </is>
+      </c>
+      <c r="O447" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 450 5565</t>
+        </is>
+      </c>
+      <c r="P447" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="Q447" s="2" t="inlineStr"/>
+      <c r="R447" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/o-reilly-s-supervalu/</t>
+        </is>
+      </c>
+      <c r="S447" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SuperValuIreland/</t>
+        </is>
+      </c>
+      <c r="T447" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supervalu_irl/</t>
+        </is>
+      </c>
+      <c r="U447" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/supervaluirl</t>
+        </is>
+      </c>
+      <c r="V447" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/SuperValuIreland</t>
+        </is>
+      </c>
+      <c r="W447" s="2" t="inlineStr">
+        <is>
+          <t>Glenn Leacy</t>
+        </is>
+      </c>
+      <c r="X447" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y447" s="2" t="inlineStr"/>
+      <c r="Z447" s="2" t="inlineStr"/>
+      <c r="AA447" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/glenn-leacy-60a89252/</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>Ardkeen Quality Food Store</t>
+        </is>
+      </c>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t>Ardkeen Quality Food Store</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>30284</t>
+        </is>
+      </c>
+      <c r="D448" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr">
+        <is>
+          <t>Waterford</t>
+        </is>
+      </c>
+      <c r="F448" s="2" t="inlineStr">
+        <is>
+          <t>County Waterford</t>
+        </is>
+      </c>
+      <c r="G448" s="2" t="inlineStr">
+        <is>
+          <t>Dunmore Road</t>
+        </is>
+      </c>
+      <c r="H448" s="2" t="inlineStr">
+        <is>
+          <t>X91 HP9W</t>
+        </is>
+      </c>
+      <c r="I448" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ardkeen.com</t>
+        </is>
+      </c>
+      <c r="J448" s="2" t="inlineStr"/>
+      <c r="K448" s="2" t="inlineStr"/>
+      <c r="L448" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M448" s="2" t="inlineStr"/>
+      <c r="N448" s="2" t="inlineStr">
+        <is>
+          <t>info@ardkeen.com</t>
+        </is>
+      </c>
+      <c r="O448" s="2" t="inlineStr">
+        <is>
+          <t>+353 51 874 620</t>
+        </is>
+      </c>
+      <c r="P448" s="2" t="inlineStr">
+        <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="Q448" s="2" t="inlineStr">
+        <is>
+          <t>45413</t>
+        </is>
+      </c>
+      <c r="R448" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ardkeen-quality-food-store/</t>
+        </is>
+      </c>
+      <c r="S448" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ardkeenqualityfoodstore</t>
+        </is>
+      </c>
+      <c r="T448" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ardkeenqualityfoodstore</t>
+        </is>
+      </c>
+      <c r="U448" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/ardkeenqfs</t>
+        </is>
+      </c>
+      <c r="V448" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCq9cEZCM7NAwDflY_yJHT5Q</t>
+        </is>
+      </c>
+      <c r="W448" s="2" t="inlineStr">
+        <is>
+          <t>Christine Fowler</t>
+        </is>
+      </c>
+      <c r="X448" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y448" s="2" t="inlineStr"/>
+      <c r="Z448" s="2" t="inlineStr"/>
+      <c r="AA448" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cfowler1</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>Bubble Brothers Limited</t>
+        </is>
+      </c>
+      <c r="B449" s="2" t="inlineStr">
+        <is>
+          <t>Bubble Brothers Limited</t>
+        </is>
+      </c>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>26091</t>
+        </is>
+      </c>
+      <c r="D449" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E449" s="2" t="inlineStr">
+        <is>
+          <t>Cork</t>
+        </is>
+      </c>
+      <c r="F449" s="2" t="inlineStr">
+        <is>
+          <t>County Cork</t>
+        </is>
+      </c>
+      <c r="G449" s="2" t="inlineStr">
+        <is>
+          <t>Marina Commercial Park, Centre Park Road</t>
+        </is>
+      </c>
+      <c r="H449" s="2" t="inlineStr">
+        <is>
+          <t>T12 ND2W</t>
+        </is>
+      </c>
+      <c r="I449" s="2" t="inlineStr">
+        <is>
+          <t>http://www.marypawlewines.com, https://bubblebrothers.ie</t>
+        </is>
+      </c>
+      <c r="J449" s="2" t="inlineStr"/>
+      <c r="K449" s="2" t="inlineStr"/>
+      <c r="L449" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M449" s="2" t="inlineStr"/>
+      <c r="N449" s="2" t="inlineStr">
+        <is>
+          <t>info@bubblebrothers.ie</t>
+        </is>
+      </c>
+      <c r="O449" s="2" t="inlineStr">
+        <is>
+          <t>+353 21 431 6000</t>
+        </is>
+      </c>
+      <c r="P449" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q449" s="2" t="inlineStr">
+        <is>
+          <t>291250</t>
+        </is>
+      </c>
+      <c r="R449" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bubble-brothers</t>
+        </is>
+      </c>
+      <c r="S449" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bubblebrothers</t>
+        </is>
+      </c>
+      <c r="T449" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bubblebrotherscork/</t>
+        </is>
+      </c>
+      <c r="U449" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/bubblebrothers</t>
+        </is>
+      </c>
+      <c r="V449" s="2" t="inlineStr"/>
+      <c r="W449" s="2" t="inlineStr">
+        <is>
+          <t>Billy Forrester</t>
+        </is>
+      </c>
+      <c r="X449" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y449" s="2" t="inlineStr"/>
+      <c r="Z449" s="2" t="inlineStr"/>
+      <c r="AA449" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/billy-forrester-a5697b36/</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>Jj Mahons &amp; Sons</t>
+        </is>
+      </c>
+      <c r="B450" s="2" t="inlineStr">
+        <is>
+          <t>Jj Mahons &amp; Sons</t>
+        </is>
+      </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>20930</t>
+        </is>
+      </c>
+      <c r="D450" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="inlineStr">
+        <is>
+          <t>Kildare</t>
+        </is>
+      </c>
+      <c r="F450" s="2" t="inlineStr">
+        <is>
+          <t>County Kildare</t>
+        </is>
+      </c>
+      <c r="G450" s="2" t="inlineStr">
+        <is>
+          <t>Cross Keys</t>
+        </is>
+      </c>
+      <c r="H450" s="2" t="inlineStr">
+        <is>
+          <t>R51 C625</t>
+        </is>
+      </c>
+      <c r="I450" s="2" t="inlineStr">
+        <is>
+          <t>http://jjmahons.com</t>
+        </is>
+      </c>
+      <c r="J450" s="2" t="inlineStr"/>
+      <c r="K450" s="2" t="inlineStr"/>
+      <c r="L450" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M450" s="2" t="inlineStr"/>
+      <c r="N450" s="2" t="inlineStr">
+        <is>
+          <t>info@jjmahons.com</t>
+        </is>
+      </c>
+      <c r="O450" s="2" t="inlineStr">
+        <is>
+          <t>+353 45 521 316</t>
+        </is>
+      </c>
+      <c r="P450" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="Q450" s="2" t="inlineStr">
+        <is>
+          <t>32542</t>
+        </is>
+      </c>
+      <c r="R450" s="2" t="inlineStr"/>
+      <c r="S450" s="2" t="inlineStr"/>
+      <c r="T450" s="2" t="inlineStr"/>
+      <c r="U450" s="2" t="inlineStr"/>
+      <c r="V450" s="2" t="inlineStr"/>
+      <c r="W450" s="2" t="inlineStr">
+        <is>
+          <t>David Mahon</t>
+        </is>
+      </c>
+      <c r="X450" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y450" s="2" t="inlineStr"/>
+      <c r="Z450" s="2" t="inlineStr"/>
+      <c r="AA450" s="2" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>Jj Mahons &amp; Sons</t>
+        </is>
+      </c>
+      <c r="B451" s="2" t="inlineStr">
+        <is>
+          <t>Jj Mahons &amp; Sons</t>
+        </is>
+      </c>
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>20930</t>
+        </is>
+      </c>
+      <c r="D451" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="inlineStr">
+        <is>
+          <t>Kildare</t>
+        </is>
+      </c>
+      <c r="F451" s="2" t="inlineStr">
+        <is>
+          <t>County Kildare</t>
+        </is>
+      </c>
+      <c r="G451" s="2" t="inlineStr">
+        <is>
+          <t>Cross Keys</t>
+        </is>
+      </c>
+      <c r="H451" s="2" t="inlineStr">
+        <is>
+          <t>R51 C625</t>
+        </is>
+      </c>
+      <c r="I451" s="2" t="inlineStr">
+        <is>
+          <t>http://jjmahons.com</t>
+        </is>
+      </c>
+      <c r="J451" s="2" t="inlineStr"/>
+      <c r="K451" s="2" t="inlineStr"/>
+      <c r="L451" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M451" s="2" t="inlineStr"/>
+      <c r="N451" s="2" t="inlineStr">
+        <is>
+          <t>info@jjmahons.com</t>
+        </is>
+      </c>
+      <c r="O451" s="2" t="inlineStr">
+        <is>
+          <t>+353 45 521 316</t>
+        </is>
+      </c>
+      <c r="P451" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="Q451" s="2" t="inlineStr">
+        <is>
+          <t>32542</t>
+        </is>
+      </c>
+      <c r="R451" s="2" t="inlineStr"/>
+      <c r="S451" s="2" t="inlineStr"/>
+      <c r="T451" s="2" t="inlineStr"/>
+      <c r="U451" s="2" t="inlineStr"/>
+      <c r="V451" s="2" t="inlineStr"/>
+      <c r="W451" s="2" t="inlineStr">
+        <is>
+          <t>Julie McMahon</t>
+        </is>
+      </c>
+      <c r="X451" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y451" s="2" t="inlineStr"/>
+      <c r="Z451" s="2" t="inlineStr"/>
+      <c r="AA451" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/julie-mcmahon-2595ab35/</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>Copsewood Limited</t>
+        </is>
+      </c>
+      <c r="B452" s="2" t="inlineStr">
+        <is>
+          <t>Copsewood Limited</t>
+        </is>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>8051</t>
+        </is>
+      </c>
+      <c r="D452" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F452" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G452" s="2" t="inlineStr">
+        <is>
+          <t>Portmarnock Town Centre,  Strand Road, Portmarnock</t>
+        </is>
+      </c>
+      <c r="H452" s="2" t="inlineStr">
+        <is>
+          <t>D13 FP28</t>
+        </is>
+      </c>
+      <c r="I452" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jusdevine.ie</t>
+        </is>
+      </c>
+      <c r="J452" s="2" t="inlineStr"/>
+      <c r="K452" s="2" t="inlineStr"/>
+      <c r="L452" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M452" s="2" t="inlineStr"/>
+      <c r="N452" s="2" t="inlineStr">
+        <is>
+          <t>info@jusdevine.ie</t>
+        </is>
+      </c>
+      <c r="O452" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 846 1192</t>
+        </is>
+      </c>
+      <c r="P452" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q452" s="2" t="inlineStr">
+        <is>
+          <t>167088</t>
+        </is>
+      </c>
+      <c r="R452" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jus-de-vine-wine-shop/</t>
+        </is>
+      </c>
+      <c r="S452" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/jusdevineportmarnock/</t>
+        </is>
+      </c>
+      <c r="T452" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jusdevine_/</t>
+        </is>
+      </c>
+      <c r="U452" s="2" t="inlineStr"/>
+      <c r="V452" s="2" t="inlineStr"/>
+      <c r="W452" s="2" t="inlineStr"/>
+      <c r="X452" s="2" t="inlineStr"/>
+      <c r="Y452" s="2" t="inlineStr"/>
+      <c r="Z452" s="2" t="inlineStr"/>
+      <c r="AA452" s="2" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>O'donovans Off Licence Limited</t>
+        </is>
+      </c>
+      <c r="B453" s="2" t="inlineStr">
+        <is>
+          <t>O'donovans Off Licence Limited</t>
+        </is>
+      </c>
+      <c r="C453" s="2" t="inlineStr">
+        <is>
+          <t>8071</t>
+        </is>
+      </c>
+      <c r="D453" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="inlineStr">
+        <is>
+          <t>Cork</t>
+        </is>
+      </c>
+      <c r="F453" s="2" t="inlineStr">
+        <is>
+          <t>Co. Cork</t>
+        </is>
+      </c>
+      <c r="G453" s="2" t="inlineStr">
+        <is>
+          <t>Cork Bonded Warehouse, Little Island Business Park, Little Island</t>
+        </is>
+      </c>
+      <c r="H453" s="2" t="inlineStr">
+        <is>
+          <t>T45 VY26</t>
+        </is>
+      </c>
+      <c r="I453" s="2" t="inlineStr">
+        <is>
+          <t>https://www.odonovansofflicence.com</t>
+        </is>
+      </c>
+      <c r="J453" s="2" t="inlineStr"/>
+      <c r="K453" s="2" t="inlineStr"/>
+      <c r="L453" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M453" s="2" t="inlineStr"/>
+      <c r="N453" s="2" t="inlineStr">
+        <is>
+          <t>info@odonovansofflicence.com</t>
+        </is>
+      </c>
+      <c r="O453" s="2" t="inlineStr">
+        <is>
+          <t>+353 21 429 6060</t>
+        </is>
+      </c>
+      <c r="P453" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q453" s="2" t="inlineStr">
+        <is>
+          <t>331387</t>
+        </is>
+      </c>
+      <c r="R453" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/o'donovans-off-licence</t>
+        </is>
+      </c>
+      <c r="S453" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/odonovansofflicences</t>
+        </is>
+      </c>
+      <c r="T453" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/odonovansofflicence</t>
+        </is>
+      </c>
+      <c r="U453" s="2" t="inlineStr"/>
+      <c r="V453" s="2" t="inlineStr"/>
+      <c r="W453" s="2" t="inlineStr">
+        <is>
+          <t>Gary O'Donovan</t>
+        </is>
+      </c>
+      <c r="X453" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y453" s="2" t="inlineStr"/>
+      <c r="Z453" s="2" t="inlineStr"/>
+      <c r="AA453" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gary-o-donovan-ba-wset-dip-59a92616/</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>Tankersley Wine Brokers Limited</t>
+        </is>
+      </c>
+      <c r="B454" s="2" t="inlineStr">
+        <is>
+          <t>Tankersley Wine Brokers Limited</t>
+        </is>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>8023</t>
+        </is>
+      </c>
+      <c r="D454" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr">
+        <is>
+          <t>Tinahely</t>
+        </is>
+      </c>
+      <c r="F454" s="2" t="inlineStr">
+        <is>
+          <t>Co. Wicklow</t>
+        </is>
+      </c>
+      <c r="G454" s="2" t="inlineStr">
+        <is>
+          <t>Tankersley Cottage, Preban</t>
+        </is>
+      </c>
+      <c r="H454" s="2" t="inlineStr">
+        <is>
+          <t>Y14 YV09</t>
+        </is>
+      </c>
+      <c r="I454" s="2" t="inlineStr">
+        <is>
+          <t>https://tankersleywine.com</t>
+        </is>
+      </c>
+      <c r="J454" s="2" t="inlineStr"/>
+      <c r="K454" s="2" t="inlineStr"/>
+      <c r="L454" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M454" s="2" t="inlineStr"/>
+      <c r="N454" s="2" t="inlineStr">
+        <is>
+          <t>info@tankersleywine.ie</t>
+        </is>
+      </c>
+      <c r="O454" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 485 2694</t>
+        </is>
+      </c>
+      <c r="P454" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q454" s="2" t="inlineStr">
+        <is>
+          <t>329628</t>
+        </is>
+      </c>
+      <c r="R454" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tankersley-wine-brokers/</t>
+        </is>
+      </c>
+      <c r="S454" s="2" t="inlineStr"/>
+      <c r="T454" s="2" t="inlineStr"/>
+      <c r="U454" s="2" t="inlineStr"/>
+      <c r="V454" s="2" t="inlineStr"/>
+      <c r="W454" s="2" t="inlineStr"/>
+      <c r="X454" s="2" t="inlineStr"/>
+      <c r="Y454" s="2" t="inlineStr"/>
+      <c r="Z454" s="2" t="inlineStr"/>
+      <c r="AA454" s="2" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>J.j. Fox Limited</t>
+        </is>
+      </c>
+      <c r="B455" s="2" t="inlineStr">
+        <is>
+          <t>J.j. Fox Limited</t>
+        </is>
+      </c>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>28785</t>
+        </is>
+      </c>
+      <c r="D455" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F455" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G455" s="2" t="inlineStr">
+        <is>
+          <t>119 Grafton Street</t>
+        </is>
+      </c>
+      <c r="H455" s="2" t="inlineStr">
+        <is>
+          <t>D02 E620</t>
+        </is>
+      </c>
+      <c r="I455" s="2" t="inlineStr">
+        <is>
+          <t>https://jamesfox.ie</t>
+        </is>
+      </c>
+      <c r="J455" s="2" t="inlineStr"/>
+      <c r="K455" s="2" t="inlineStr"/>
+      <c r="L455" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M455" s="2" t="inlineStr"/>
+      <c r="N455" s="2" t="inlineStr">
+        <is>
+          <t>info@jamesfox.ie</t>
+        </is>
+      </c>
+      <c r="O455" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 677 0533</t>
+        </is>
+      </c>
+      <c r="P455" s="2" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="Q455" s="2" t="inlineStr">
+        <is>
+          <t>9864</t>
+        </is>
+      </c>
+      <c r="R455" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/james-fox-cigar-&amp;-whiskey-store</t>
+        </is>
+      </c>
+      <c r="S455" s="2" t="inlineStr"/>
+      <c r="T455" s="2" t="inlineStr"/>
+      <c r="U455" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/jamesfoxdublin</t>
+        </is>
+      </c>
+      <c r="V455" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/JamesJFoxDublin</t>
+        </is>
+      </c>
+      <c r="W455" s="2" t="inlineStr">
+        <is>
+          <t>Yiorgos Manesis</t>
+        </is>
+      </c>
+      <c r="X455" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y455" s="2" t="inlineStr"/>
+      <c r="Z455" s="2" t="inlineStr"/>
+      <c r="AA455" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/yiorgosmanesis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>J.j. Fox Limited</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="inlineStr">
+        <is>
+          <t>J.j. Fox Limited</t>
+        </is>
+      </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>28785</t>
+        </is>
+      </c>
+      <c r="D456" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F456" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G456" s="2" t="inlineStr">
+        <is>
+          <t>119 Grafton Street</t>
+        </is>
+      </c>
+      <c r="H456" s="2" t="inlineStr">
+        <is>
+          <t>D02 E620</t>
+        </is>
+      </c>
+      <c r="I456" s="2" t="inlineStr">
+        <is>
+          <t>https://jamesfox.ie</t>
+        </is>
+      </c>
+      <c r="J456" s="2" t="inlineStr"/>
+      <c r="K456" s="2" t="inlineStr"/>
+      <c r="L456" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M456" s="2" t="inlineStr"/>
+      <c r="N456" s="2" t="inlineStr">
+        <is>
+          <t>info@jamesfox.ie</t>
+        </is>
+      </c>
+      <c r="O456" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 677 0533</t>
+        </is>
+      </c>
+      <c r="P456" s="2" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="Q456" s="2" t="inlineStr">
+        <is>
+          <t>9864</t>
+        </is>
+      </c>
+      <c r="R456" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/james-fox-cigar-&amp;-whiskey-store</t>
+        </is>
+      </c>
+      <c r="S456" s="2" t="inlineStr"/>
+      <c r="T456" s="2" t="inlineStr"/>
+      <c r="U456" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/jamesfoxdublin</t>
+        </is>
+      </c>
+      <c r="V456" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/JamesJFoxDublin</t>
+        </is>
+      </c>
+      <c r="W456" s="2" t="inlineStr">
+        <is>
+          <t>Amy Catherine</t>
+        </is>
+      </c>
+      <c r="X456" s="2" t="inlineStr">
+        <is>
+          <t>Sales Executive</t>
+        </is>
+      </c>
+      <c r="Y456" s="2" t="inlineStr"/>
+      <c r="Z456" s="2" t="inlineStr"/>
+      <c r="AA456" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/amy-catherine-mcloughlin-4246a819a/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Ireland.xlsx
+++ b/BWI/bestwine_output/bestwine_Ireland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA456"/>
+  <dimension ref="A1:AA471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -49642,6 +49642,1497 @@
         </is>
       </c>
     </row>
+    <row r="457">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>L.CONNAUGHTON &amp; SONS LIMITED</t>
+        </is>
+      </c>
+      <c r="B457" s="2" t="inlineStr"/>
+      <c r="C457" s="2" t="inlineStr">
+        <is>
+          <t>168832</t>
+        </is>
+      </c>
+      <c r="D457" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E457" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F457" s="2" t="inlineStr"/>
+      <c r="G457" s="2" t="inlineStr">
+        <is>
+          <t>Unit 7 Willsborough Industrial Estate</t>
+        </is>
+      </c>
+      <c r="H457" s="2" t="inlineStr">
+        <is>
+          <t>D17 W304</t>
+        </is>
+      </c>
+      <c r="I457" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lconnaughton.ie</t>
+        </is>
+      </c>
+      <c r="J457" s="2" t="inlineStr"/>
+      <c r="K457" s="2" t="inlineStr"/>
+      <c r="L457" s="2" t="inlineStr"/>
+      <c r="M457" s="2" t="inlineStr"/>
+      <c r="N457" s="2" t="inlineStr">
+        <is>
+          <t>info@lconnaughton.ie</t>
+        </is>
+      </c>
+      <c r="O457" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 671 3243</t>
+        </is>
+      </c>
+      <c r="P457" s="2" t="inlineStr"/>
+      <c r="Q457" s="2" t="inlineStr"/>
+      <c r="R457" s="2" t="inlineStr"/>
+      <c r="S457" s="2" t="inlineStr"/>
+      <c r="T457" s="2" t="inlineStr"/>
+      <c r="U457" s="2" t="inlineStr"/>
+      <c r="V457" s="2" t="inlineStr"/>
+      <c r="W457" s="2" t="inlineStr"/>
+      <c r="X457" s="2" t="inlineStr"/>
+      <c r="Y457" s="2" t="inlineStr"/>
+      <c r="Z457" s="2" t="inlineStr"/>
+      <c r="AA457" s="2" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>Maccurtain Wine Cellar</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t>Maccurtain Wine Cellar</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>122609</t>
+        </is>
+      </c>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="inlineStr">
+        <is>
+          <t>Cork</t>
+        </is>
+      </c>
+      <c r="F458" s="2" t="inlineStr">
+        <is>
+          <t>County Cork</t>
+        </is>
+      </c>
+      <c r="G458" s="2" t="inlineStr">
+        <is>
+          <t>11 MacCurtain Street, Victorian Quarter</t>
+        </is>
+      </c>
+      <c r="H458" s="2" t="inlineStr">
+        <is>
+          <t>T23 FR66</t>
+        </is>
+      </c>
+      <c r="I458" s="2" t="inlineStr">
+        <is>
+          <t>https://maccurtainwine.ie</t>
+        </is>
+      </c>
+      <c r="J458" s="2" t="inlineStr"/>
+      <c r="K458" s="2" t="inlineStr"/>
+      <c r="L458" s="2" t="inlineStr"/>
+      <c r="M458" s="2" t="inlineStr"/>
+      <c r="N458" s="2" t="inlineStr">
+        <is>
+          <t>info@maccurtainwine.ie</t>
+        </is>
+      </c>
+      <c r="O458" s="2" t="inlineStr">
+        <is>
+          <t>+353 21 455 1533</t>
+        </is>
+      </c>
+      <c r="P458" s="2" t="inlineStr"/>
+      <c r="Q458" s="2" t="inlineStr"/>
+      <c r="R458" s="2" t="inlineStr"/>
+      <c r="S458" s="2" t="inlineStr"/>
+      <c r="T458" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maccurtainwinecellar/</t>
+        </is>
+      </c>
+      <c r="U458" s="2" t="inlineStr"/>
+      <c r="V458" s="2" t="inlineStr"/>
+      <c r="W458" s="2" t="inlineStr">
+        <is>
+          <t>Craig Horgan</t>
+        </is>
+      </c>
+      <c r="X458" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y458" s="2" t="inlineStr"/>
+      <c r="Z458" s="2" t="inlineStr"/>
+      <c r="AA458" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/craig-horgan-78203b100/</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>The Grapevine Off Licence</t>
+        </is>
+      </c>
+      <c r="B459" s="2" t="inlineStr">
+        <is>
+          <t>The Grapevine Off Licence</t>
+        </is>
+      </c>
+      <c r="C459" s="2" t="inlineStr">
+        <is>
+          <t>122605</t>
+        </is>
+      </c>
+      <c r="D459" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E459" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 9</t>
+        </is>
+      </c>
+      <c r="F459" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G459" s="2" t="inlineStr">
+        <is>
+          <t>82 Ballymun Road, Glasnevin</t>
+        </is>
+      </c>
+      <c r="H459" s="2" t="inlineStr">
+        <is>
+          <t>D09 PX93</t>
+        </is>
+      </c>
+      <c r="I459" s="2" t="inlineStr">
+        <is>
+          <t>https://thegrapevinedublin.ie</t>
+        </is>
+      </c>
+      <c r="J459" s="2" t="inlineStr"/>
+      <c r="K459" s="2" t="inlineStr"/>
+      <c r="L459" s="2" t="inlineStr"/>
+      <c r="M459" s="2" t="inlineStr"/>
+      <c r="N459" s="2" t="inlineStr">
+        <is>
+          <t>thegrapevineofflicence@gmail.com</t>
+        </is>
+      </c>
+      <c r="O459" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 884 4988</t>
+        </is>
+      </c>
+      <c r="P459" s="2" t="inlineStr"/>
+      <c r="Q459" s="2" t="inlineStr"/>
+      <c r="R459" s="2" t="inlineStr"/>
+      <c r="S459" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TheGrapeVineOffLicence</t>
+        </is>
+      </c>
+      <c r="T459" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thegrapevinedublin</t>
+        </is>
+      </c>
+      <c r="U459" s="2" t="inlineStr"/>
+      <c r="V459" s="2" t="inlineStr"/>
+      <c r="W459" s="2" t="inlineStr"/>
+      <c r="X459" s="2" t="inlineStr"/>
+      <c r="Y459" s="2" t="inlineStr"/>
+      <c r="Z459" s="2" t="inlineStr"/>
+      <c r="AA459" s="2" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>Valeo Foods Ireland</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t>Valeo Foods Ireland</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>7976</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F460" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>79 Broomhill Road, Tallaght</t>
+        </is>
+      </c>
+      <c r="H460" s="2" t="inlineStr">
+        <is>
+          <t>D24 AV9R</t>
+        </is>
+      </c>
+      <c r="I460" s="2" t="inlineStr">
+        <is>
+          <t>https://www.findlaterandco.com</t>
+        </is>
+      </c>
+      <c r="J460" s="2" t="inlineStr"/>
+      <c r="K460" s="2" t="inlineStr"/>
+      <c r="L460" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M460" s="2" t="inlineStr"/>
+      <c r="N460" s="2" t="inlineStr">
+        <is>
+          <t>info@findlaterandco.com</t>
+        </is>
+      </c>
+      <c r="O460" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 404 7300</t>
+        </is>
+      </c>
+      <c r="P460" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q460" s="2" t="inlineStr"/>
+      <c r="R460" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/findlater-co/</t>
+        </is>
+      </c>
+      <c r="S460" s="2" t="inlineStr"/>
+      <c r="T460" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/findlater_and_co</t>
+        </is>
+      </c>
+      <c r="U460" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/FindlaterandCo</t>
+        </is>
+      </c>
+      <c r="V460" s="2" t="inlineStr"/>
+      <c r="W460" s="2" t="inlineStr">
+        <is>
+          <t>Richard Moriarty</t>
+        </is>
+      </c>
+      <c r="X460" s="2" t="inlineStr">
+        <is>
+          <t>Wine &amp; Spirit Director</t>
+        </is>
+      </c>
+      <c r="Y460" s="2" t="inlineStr"/>
+      <c r="Z460" s="2" t="inlineStr"/>
+      <c r="AA460" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rimoriarty/</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>Valeo Foods Ireland</t>
+        </is>
+      </c>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <t>Valeo Foods Ireland</t>
+        </is>
+      </c>
+      <c r="C461" s="2" t="inlineStr">
+        <is>
+          <t>7976</t>
+        </is>
+      </c>
+      <c r="D461" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E461" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F461" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G461" s="2" t="inlineStr">
+        <is>
+          <t>79 Broomhill Road, Tallaght</t>
+        </is>
+      </c>
+      <c r="H461" s="2" t="inlineStr">
+        <is>
+          <t>D24 AV9R</t>
+        </is>
+      </c>
+      <c r="I461" s="2" t="inlineStr">
+        <is>
+          <t>https://www.findlaterandco.com</t>
+        </is>
+      </c>
+      <c r="J461" s="2" t="inlineStr"/>
+      <c r="K461" s="2" t="inlineStr"/>
+      <c r="L461" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M461" s="2" t="inlineStr"/>
+      <c r="N461" s="2" t="inlineStr">
+        <is>
+          <t>info@findlaterandco.com</t>
+        </is>
+      </c>
+      <c r="O461" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 404 7300</t>
+        </is>
+      </c>
+      <c r="P461" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q461" s="2" t="inlineStr"/>
+      <c r="R461" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/findlater-co/</t>
+        </is>
+      </c>
+      <c r="S461" s="2" t="inlineStr"/>
+      <c r="T461" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/findlater_and_co</t>
+        </is>
+      </c>
+      <c r="U461" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/FindlaterandCo</t>
+        </is>
+      </c>
+      <c r="V461" s="2" t="inlineStr"/>
+      <c r="W461" s="2" t="inlineStr">
+        <is>
+          <t>Declan Bonner</t>
+        </is>
+      </c>
+      <c r="X461" s="2" t="inlineStr">
+        <is>
+          <t>Wine Specialist</t>
+        </is>
+      </c>
+      <c r="Y461" s="2" t="inlineStr"/>
+      <c r="Z461" s="2" t="inlineStr"/>
+      <c r="AA461" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/declan-bonner-8082205b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>Supervalu Ireland</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>Supervalu Ireland</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>108273</t>
+        </is>
+      </c>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 12</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G462" s="2" t="inlineStr">
+        <is>
+          <t>Walkinstown</t>
+        </is>
+      </c>
+      <c r="H462" s="2" t="inlineStr">
+        <is>
+          <t>D12 XDK2</t>
+        </is>
+      </c>
+      <c r="I462" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.supervalu.ie, https://supervalu.ie</t>
+        </is>
+      </c>
+      <c r="J462" s="2" t="inlineStr"/>
+      <c r="K462" s="2" t="inlineStr"/>
+      <c r="L462" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M462" s="2" t="inlineStr"/>
+      <c r="N462" s="2" t="inlineStr">
+        <is>
+          <t>hannonenfield@supervalu.ie</t>
+        </is>
+      </c>
+      <c r="O462" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 450 5565</t>
+        </is>
+      </c>
+      <c r="P462" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="Q462" s="2" t="inlineStr"/>
+      <c r="R462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/o-reilly-s-supervalu/</t>
+        </is>
+      </c>
+      <c r="S462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SuperValuIreland/</t>
+        </is>
+      </c>
+      <c r="T462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supervalu_irl/</t>
+        </is>
+      </c>
+      <c r="U462" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/supervaluirl</t>
+        </is>
+      </c>
+      <c r="V462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/SuperValuIreland</t>
+        </is>
+      </c>
+      <c r="W462" s="2" t="inlineStr">
+        <is>
+          <t>Glenn Leacy</t>
+        </is>
+      </c>
+      <c r="X462" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y462" s="2" t="inlineStr"/>
+      <c r="Z462" s="2" t="inlineStr"/>
+      <c r="AA462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/glenn-leacy-60a89252/</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>Ardkeen Quality Food Store</t>
+        </is>
+      </c>
+      <c r="B463" s="2" t="inlineStr">
+        <is>
+          <t>Ardkeen Quality Food Store</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
+          <t>30284</t>
+        </is>
+      </c>
+      <c r="D463" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="inlineStr">
+        <is>
+          <t>Waterford</t>
+        </is>
+      </c>
+      <c r="F463" s="2" t="inlineStr">
+        <is>
+          <t>County Waterford</t>
+        </is>
+      </c>
+      <c r="G463" s="2" t="inlineStr">
+        <is>
+          <t>Dunmore Road</t>
+        </is>
+      </c>
+      <c r="H463" s="2" t="inlineStr">
+        <is>
+          <t>X91 HP9W</t>
+        </is>
+      </c>
+      <c r="I463" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ardkeen.com</t>
+        </is>
+      </c>
+      <c r="J463" s="2" t="inlineStr"/>
+      <c r="K463" s="2" t="inlineStr"/>
+      <c r="L463" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M463" s="2" t="inlineStr"/>
+      <c r="N463" s="2" t="inlineStr">
+        <is>
+          <t>info@ardkeen.com</t>
+        </is>
+      </c>
+      <c r="O463" s="2" t="inlineStr">
+        <is>
+          <t>+353 51 874 620</t>
+        </is>
+      </c>
+      <c r="P463" s="2" t="inlineStr">
+        <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="Q463" s="2" t="inlineStr">
+        <is>
+          <t>45413</t>
+        </is>
+      </c>
+      <c r="R463" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ardkeen-quality-food-store/</t>
+        </is>
+      </c>
+      <c r="S463" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ardkeenqualityfoodstore</t>
+        </is>
+      </c>
+      <c r="T463" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ardkeenqualityfoodstore</t>
+        </is>
+      </c>
+      <c r="U463" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/ardkeenqfs</t>
+        </is>
+      </c>
+      <c r="V463" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCq9cEZCM7NAwDflY_yJHT5Q</t>
+        </is>
+      </c>
+      <c r="W463" s="2" t="inlineStr">
+        <is>
+          <t>Christine Fowler</t>
+        </is>
+      </c>
+      <c r="X463" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y463" s="2" t="inlineStr"/>
+      <c r="Z463" s="2" t="inlineStr"/>
+      <c r="AA463" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cfowler1</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>Bubble Brothers Limited</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t>Bubble Brothers Limited</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>26091</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="inlineStr">
+        <is>
+          <t>Cork</t>
+        </is>
+      </c>
+      <c r="F464" s="2" t="inlineStr">
+        <is>
+          <t>County Cork</t>
+        </is>
+      </c>
+      <c r="G464" s="2" t="inlineStr">
+        <is>
+          <t>Marina Commercial Park, Centre Park Road</t>
+        </is>
+      </c>
+      <c r="H464" s="2" t="inlineStr">
+        <is>
+          <t>T12 ND2W</t>
+        </is>
+      </c>
+      <c r="I464" s="2" t="inlineStr">
+        <is>
+          <t>http://www.marypawlewines.com, https://bubblebrothers.ie</t>
+        </is>
+      </c>
+      <c r="J464" s="2" t="inlineStr"/>
+      <c r="K464" s="2" t="inlineStr"/>
+      <c r="L464" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M464" s="2" t="inlineStr"/>
+      <c r="N464" s="2" t="inlineStr">
+        <is>
+          <t>info@bubblebrothers.ie</t>
+        </is>
+      </c>
+      <c r="O464" s="2" t="inlineStr">
+        <is>
+          <t>+353 21 431 6000</t>
+        </is>
+      </c>
+      <c r="P464" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q464" s="2" t="inlineStr">
+        <is>
+          <t>291250</t>
+        </is>
+      </c>
+      <c r="R464" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bubble-brothers</t>
+        </is>
+      </c>
+      <c r="S464" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bubblebrothers</t>
+        </is>
+      </c>
+      <c r="T464" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bubblebrotherscork/</t>
+        </is>
+      </c>
+      <c r="U464" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/bubblebrothers</t>
+        </is>
+      </c>
+      <c r="V464" s="2" t="inlineStr"/>
+      <c r="W464" s="2" t="inlineStr">
+        <is>
+          <t>Billy Forrester</t>
+        </is>
+      </c>
+      <c r="X464" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y464" s="2" t="inlineStr"/>
+      <c r="Z464" s="2" t="inlineStr"/>
+      <c r="AA464" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/billy-forrester-a5697b36/</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>Jj Mahons &amp; Sons</t>
+        </is>
+      </c>
+      <c r="B465" s="2" t="inlineStr">
+        <is>
+          <t>Jj Mahons &amp; Sons</t>
+        </is>
+      </c>
+      <c r="C465" s="2" t="inlineStr">
+        <is>
+          <t>20930</t>
+        </is>
+      </c>
+      <c r="D465" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E465" s="2" t="inlineStr">
+        <is>
+          <t>Kildare</t>
+        </is>
+      </c>
+      <c r="F465" s="2" t="inlineStr">
+        <is>
+          <t>County Kildare</t>
+        </is>
+      </c>
+      <c r="G465" s="2" t="inlineStr">
+        <is>
+          <t>Cross Keys</t>
+        </is>
+      </c>
+      <c r="H465" s="2" t="inlineStr">
+        <is>
+          <t>R51 C625</t>
+        </is>
+      </c>
+      <c r="I465" s="2" t="inlineStr">
+        <is>
+          <t>http://jjmahons.com</t>
+        </is>
+      </c>
+      <c r="J465" s="2" t="inlineStr"/>
+      <c r="K465" s="2" t="inlineStr"/>
+      <c r="L465" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M465" s="2" t="inlineStr"/>
+      <c r="N465" s="2" t="inlineStr">
+        <is>
+          <t>info@jjmahons.com</t>
+        </is>
+      </c>
+      <c r="O465" s="2" t="inlineStr">
+        <is>
+          <t>+353 45 521 316</t>
+        </is>
+      </c>
+      <c r="P465" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="Q465" s="2" t="inlineStr">
+        <is>
+          <t>32542</t>
+        </is>
+      </c>
+      <c r="R465" s="2" t="inlineStr"/>
+      <c r="S465" s="2" t="inlineStr"/>
+      <c r="T465" s="2" t="inlineStr"/>
+      <c r="U465" s="2" t="inlineStr"/>
+      <c r="V465" s="2" t="inlineStr"/>
+      <c r="W465" s="2" t="inlineStr">
+        <is>
+          <t>David Mahon</t>
+        </is>
+      </c>
+      <c r="X465" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y465" s="2" t="inlineStr"/>
+      <c r="Z465" s="2" t="inlineStr"/>
+      <c r="AA465" s="2" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>Jj Mahons &amp; Sons</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>Jj Mahons &amp; Sons</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>20930</t>
+        </is>
+      </c>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>Kildare</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>County Kildare</t>
+        </is>
+      </c>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>Cross Keys</t>
+        </is>
+      </c>
+      <c r="H466" s="2" t="inlineStr">
+        <is>
+          <t>R51 C625</t>
+        </is>
+      </c>
+      <c r="I466" s="2" t="inlineStr">
+        <is>
+          <t>http://jjmahons.com</t>
+        </is>
+      </c>
+      <c r="J466" s="2" t="inlineStr"/>
+      <c r="K466" s="2" t="inlineStr"/>
+      <c r="L466" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M466" s="2" t="inlineStr"/>
+      <c r="N466" s="2" t="inlineStr">
+        <is>
+          <t>info@jjmahons.com</t>
+        </is>
+      </c>
+      <c r="O466" s="2" t="inlineStr">
+        <is>
+          <t>+353 45 521 316</t>
+        </is>
+      </c>
+      <c r="P466" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="Q466" s="2" t="inlineStr">
+        <is>
+          <t>32542</t>
+        </is>
+      </c>
+      <c r="R466" s="2" t="inlineStr"/>
+      <c r="S466" s="2" t="inlineStr"/>
+      <c r="T466" s="2" t="inlineStr"/>
+      <c r="U466" s="2" t="inlineStr"/>
+      <c r="V466" s="2" t="inlineStr"/>
+      <c r="W466" s="2" t="inlineStr">
+        <is>
+          <t>Julie McMahon</t>
+        </is>
+      </c>
+      <c r="X466" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y466" s="2" t="inlineStr"/>
+      <c r="Z466" s="2" t="inlineStr"/>
+      <c r="AA466" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/julie-mcmahon-2595ab35/</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>Copsewood Limited</t>
+        </is>
+      </c>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t>Copsewood Limited</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>8051</t>
+        </is>
+      </c>
+      <c r="D467" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E467" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F467" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G467" s="2" t="inlineStr">
+        <is>
+          <t>Portmarnock Town Centre,  Strand Road, Portmarnock</t>
+        </is>
+      </c>
+      <c r="H467" s="2" t="inlineStr">
+        <is>
+          <t>D13 FP28</t>
+        </is>
+      </c>
+      <c r="I467" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jusdevine.ie</t>
+        </is>
+      </c>
+      <c r="J467" s="2" t="inlineStr"/>
+      <c r="K467" s="2" t="inlineStr"/>
+      <c r="L467" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M467" s="2" t="inlineStr"/>
+      <c r="N467" s="2" t="inlineStr">
+        <is>
+          <t>info@jusdevine.ie</t>
+        </is>
+      </c>
+      <c r="O467" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 846 1192</t>
+        </is>
+      </c>
+      <c r="P467" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q467" s="2" t="inlineStr">
+        <is>
+          <t>167088</t>
+        </is>
+      </c>
+      <c r="R467" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jus-de-vine-wine-shop/</t>
+        </is>
+      </c>
+      <c r="S467" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/jusdevineportmarnock/</t>
+        </is>
+      </c>
+      <c r="T467" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jusdevine_/</t>
+        </is>
+      </c>
+      <c r="U467" s="2" t="inlineStr"/>
+      <c r="V467" s="2" t="inlineStr"/>
+      <c r="W467" s="2" t="inlineStr"/>
+      <c r="X467" s="2" t="inlineStr"/>
+      <c r="Y467" s="2" t="inlineStr"/>
+      <c r="Z467" s="2" t="inlineStr"/>
+      <c r="AA467" s="2" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>O'donovans Off Licence Limited</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>O'donovans Off Licence Limited</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>8071</t>
+        </is>
+      </c>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>Cork</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
+        <is>
+          <t>Co. Cork</t>
+        </is>
+      </c>
+      <c r="G468" s="2" t="inlineStr">
+        <is>
+          <t>Cork Bonded Warehouse, Little Island Business Park, Little Island</t>
+        </is>
+      </c>
+      <c r="H468" s="2" t="inlineStr">
+        <is>
+          <t>T45 VY26</t>
+        </is>
+      </c>
+      <c r="I468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.odonovansofflicence.com</t>
+        </is>
+      </c>
+      <c r="J468" s="2" t="inlineStr"/>
+      <c r="K468" s="2" t="inlineStr"/>
+      <c r="L468" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M468" s="2" t="inlineStr"/>
+      <c r="N468" s="2" t="inlineStr">
+        <is>
+          <t>info@odonovansofflicence.com</t>
+        </is>
+      </c>
+      <c r="O468" s="2" t="inlineStr">
+        <is>
+          <t>+353 21 429 6060</t>
+        </is>
+      </c>
+      <c r="P468" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q468" s="2" t="inlineStr">
+        <is>
+          <t>331387</t>
+        </is>
+      </c>
+      <c r="R468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/o'donovans-off-licence</t>
+        </is>
+      </c>
+      <c r="S468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/odonovansofflicences</t>
+        </is>
+      </c>
+      <c r="T468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/odonovansofflicence</t>
+        </is>
+      </c>
+      <c r="U468" s="2" t="inlineStr"/>
+      <c r="V468" s="2" t="inlineStr"/>
+      <c r="W468" s="2" t="inlineStr">
+        <is>
+          <t>Gary O'Donovan</t>
+        </is>
+      </c>
+      <c r="X468" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y468" s="2" t="inlineStr"/>
+      <c r="Z468" s="2" t="inlineStr"/>
+      <c r="AA468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gary-o-donovan-ba-wset-dip-59a92616/</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>Tankersley Wine Brokers Limited</t>
+        </is>
+      </c>
+      <c r="B469" s="2" t="inlineStr">
+        <is>
+          <t>Tankersley Wine Brokers Limited</t>
+        </is>
+      </c>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>8023</t>
+        </is>
+      </c>
+      <c r="D469" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E469" s="2" t="inlineStr">
+        <is>
+          <t>Tinahely</t>
+        </is>
+      </c>
+      <c r="F469" s="2" t="inlineStr">
+        <is>
+          <t>Co. Wicklow</t>
+        </is>
+      </c>
+      <c r="G469" s="2" t="inlineStr">
+        <is>
+          <t>Tankersley Cottage, Preban</t>
+        </is>
+      </c>
+      <c r="H469" s="2" t="inlineStr">
+        <is>
+          <t>Y14 YV09</t>
+        </is>
+      </c>
+      <c r="I469" s="2" t="inlineStr">
+        <is>
+          <t>https://tankersleywine.com</t>
+        </is>
+      </c>
+      <c r="J469" s="2" t="inlineStr"/>
+      <c r="K469" s="2" t="inlineStr"/>
+      <c r="L469" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M469" s="2" t="inlineStr"/>
+      <c r="N469" s="2" t="inlineStr">
+        <is>
+          <t>info@tankersleywine.ie</t>
+        </is>
+      </c>
+      <c r="O469" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 485 2694</t>
+        </is>
+      </c>
+      <c r="P469" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q469" s="2" t="inlineStr">
+        <is>
+          <t>329628</t>
+        </is>
+      </c>
+      <c r="R469" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tankersley-wine-brokers/</t>
+        </is>
+      </c>
+      <c r="S469" s="2" t="inlineStr"/>
+      <c r="T469" s="2" t="inlineStr"/>
+      <c r="U469" s="2" t="inlineStr"/>
+      <c r="V469" s="2" t="inlineStr"/>
+      <c r="W469" s="2" t="inlineStr"/>
+      <c r="X469" s="2" t="inlineStr"/>
+      <c r="Y469" s="2" t="inlineStr"/>
+      <c r="Z469" s="2" t="inlineStr"/>
+      <c r="AA469" s="2" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>J.j. Fox Limited</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>J.j. Fox Limited</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>28785</t>
+        </is>
+      </c>
+      <c r="D470" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F470" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G470" s="2" t="inlineStr">
+        <is>
+          <t>119 Grafton Street</t>
+        </is>
+      </c>
+      <c r="H470" s="2" t="inlineStr">
+        <is>
+          <t>D02 E620</t>
+        </is>
+      </c>
+      <c r="I470" s="2" t="inlineStr">
+        <is>
+          <t>https://jamesfox.ie</t>
+        </is>
+      </c>
+      <c r="J470" s="2" t="inlineStr"/>
+      <c r="K470" s="2" t="inlineStr"/>
+      <c r="L470" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M470" s="2" t="inlineStr"/>
+      <c r="N470" s="2" t="inlineStr">
+        <is>
+          <t>info@jamesfox.ie</t>
+        </is>
+      </c>
+      <c r="O470" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 677 0533</t>
+        </is>
+      </c>
+      <c r="P470" s="2" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="Q470" s="2" t="inlineStr">
+        <is>
+          <t>9864</t>
+        </is>
+      </c>
+      <c r="R470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/james-fox-cigar-&amp;-whiskey-store</t>
+        </is>
+      </c>
+      <c r="S470" s="2" t="inlineStr"/>
+      <c r="T470" s="2" t="inlineStr"/>
+      <c r="U470" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/jamesfoxdublin</t>
+        </is>
+      </c>
+      <c r="V470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/JamesJFoxDublin</t>
+        </is>
+      </c>
+      <c r="W470" s="2" t="inlineStr">
+        <is>
+          <t>Yiorgos Manesis</t>
+        </is>
+      </c>
+      <c r="X470" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y470" s="2" t="inlineStr"/>
+      <c r="Z470" s="2" t="inlineStr"/>
+      <c r="AA470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/yiorgosmanesis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>J.j. Fox Limited</t>
+        </is>
+      </c>
+      <c r="B471" s="2" t="inlineStr">
+        <is>
+          <t>J.j. Fox Limited</t>
+        </is>
+      </c>
+      <c r="C471" s="2" t="inlineStr">
+        <is>
+          <t>28785</t>
+        </is>
+      </c>
+      <c r="D471" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F471" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G471" s="2" t="inlineStr">
+        <is>
+          <t>119 Grafton Street</t>
+        </is>
+      </c>
+      <c r="H471" s="2" t="inlineStr">
+        <is>
+          <t>D02 E620</t>
+        </is>
+      </c>
+      <c r="I471" s="2" t="inlineStr">
+        <is>
+          <t>https://jamesfox.ie</t>
+        </is>
+      </c>
+      <c r="J471" s="2" t="inlineStr"/>
+      <c r="K471" s="2" t="inlineStr"/>
+      <c r="L471" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M471" s="2" t="inlineStr"/>
+      <c r="N471" s="2" t="inlineStr">
+        <is>
+          <t>info@jamesfox.ie</t>
+        </is>
+      </c>
+      <c r="O471" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 677 0533</t>
+        </is>
+      </c>
+      <c r="P471" s="2" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="Q471" s="2" t="inlineStr">
+        <is>
+          <t>9864</t>
+        </is>
+      </c>
+      <c r="R471" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/james-fox-cigar-&amp;-whiskey-store</t>
+        </is>
+      </c>
+      <c r="S471" s="2" t="inlineStr"/>
+      <c r="T471" s="2" t="inlineStr"/>
+      <c r="U471" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/jamesfoxdublin</t>
+        </is>
+      </c>
+      <c r="V471" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/JamesJFoxDublin</t>
+        </is>
+      </c>
+      <c r="W471" s="2" t="inlineStr">
+        <is>
+          <t>Amy Catherine</t>
+        </is>
+      </c>
+      <c r="X471" s="2" t="inlineStr">
+        <is>
+          <t>Sales Executive</t>
+        </is>
+      </c>
+      <c r="Y471" s="2" t="inlineStr"/>
+      <c r="Z471" s="2" t="inlineStr"/>
+      <c r="AA471" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/amy-catherine-mcloughlin-4246a819a/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Ireland.xlsx
+++ b/BWI/bestwine_output/bestwine_Ireland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA471"/>
+  <dimension ref="A1:AA486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -51133,6 +51133,1525 @@
         </is>
       </c>
     </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>The Counter Deli</t>
+        </is>
+      </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>The Counter Deli</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>122614</t>
+        </is>
+      </c>
+      <c r="D472" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>Letterkenny</t>
+        </is>
+      </c>
+      <c r="F472" s="2" t="inlineStr">
+        <is>
+          <t>County Donegal</t>
+        </is>
+      </c>
+      <c r="G472" s="2" t="inlineStr">
+        <is>
+          <t>Canal Road, Letterkenny</t>
+        </is>
+      </c>
+      <c r="H472" s="2" t="inlineStr">
+        <is>
+          <t>F92 E8ND</t>
+        </is>
+      </c>
+      <c r="I472" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thecounterdeli.com</t>
+        </is>
+      </c>
+      <c r="J472" s="2" t="inlineStr"/>
+      <c r="K472" s="2" t="inlineStr"/>
+      <c r="L472" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M472" s="2" t="inlineStr"/>
+      <c r="N472" s="2" t="inlineStr">
+        <is>
+          <t>info@thecounterdeli.com</t>
+        </is>
+      </c>
+      <c r="O472" s="2" t="inlineStr">
+        <is>
+          <t>+353 74 912 0075</t>
+        </is>
+      </c>
+      <c r="P472" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q472" s="2" t="inlineStr"/>
+      <c r="R472" s="2" t="inlineStr"/>
+      <c r="S472" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/thecounterdeliireland/</t>
+        </is>
+      </c>
+      <c r="T472" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thecounterdeli/</t>
+        </is>
+      </c>
+      <c r="U472" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/thecounterdeli</t>
+        </is>
+      </c>
+      <c r="V472" s="2" t="inlineStr"/>
+      <c r="W472" s="2" t="inlineStr"/>
+      <c r="X472" s="2" t="inlineStr"/>
+      <c r="Y472" s="2" t="inlineStr"/>
+      <c r="Z472" s="2" t="inlineStr"/>
+      <c r="AA472" s="2" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>Maccurtain Wine Cellar</t>
+        </is>
+      </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>Maccurtain Wine Cellar</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>122609</t>
+        </is>
+      </c>
+      <c r="D473" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="inlineStr">
+        <is>
+          <t>Cork</t>
+        </is>
+      </c>
+      <c r="F473" s="2" t="inlineStr">
+        <is>
+          <t>County Cork</t>
+        </is>
+      </c>
+      <c r="G473" s="2" t="inlineStr">
+        <is>
+          <t>11 MacCurtain Street, Victorian Quarter</t>
+        </is>
+      </c>
+      <c r="H473" s="2" t="inlineStr">
+        <is>
+          <t>T23 FR66</t>
+        </is>
+      </c>
+      <c r="I473" s="2" t="inlineStr">
+        <is>
+          <t>https://maccurtainwine.ie</t>
+        </is>
+      </c>
+      <c r="J473" s="2" t="inlineStr"/>
+      <c r="K473" s="2" t="inlineStr"/>
+      <c r="L473" s="2" t="inlineStr"/>
+      <c r="M473" s="2" t="inlineStr"/>
+      <c r="N473" s="2" t="inlineStr">
+        <is>
+          <t>info@maccurtainwine.ie</t>
+        </is>
+      </c>
+      <c r="O473" s="2" t="inlineStr">
+        <is>
+          <t>+353 21 455 1533</t>
+        </is>
+      </c>
+      <c r="P473" s="2" t="inlineStr"/>
+      <c r="Q473" s="2" t="inlineStr"/>
+      <c r="R473" s="2" t="inlineStr"/>
+      <c r="S473" s="2" t="inlineStr"/>
+      <c r="T473" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maccurtainwinecellar/</t>
+        </is>
+      </c>
+      <c r="U473" s="2" t="inlineStr"/>
+      <c r="V473" s="2" t="inlineStr"/>
+      <c r="W473" s="2" t="inlineStr">
+        <is>
+          <t>Craig Horgan</t>
+        </is>
+      </c>
+      <c r="X473" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y473" s="2" t="inlineStr"/>
+      <c r="Z473" s="2" t="inlineStr"/>
+      <c r="AA473" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/craig-horgan-78203b100/</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>The Grapevine Off Licence</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>The Grapevine Off Licence</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>122605</t>
+        </is>
+      </c>
+      <c r="D474" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 9</t>
+        </is>
+      </c>
+      <c r="F474" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G474" s="2" t="inlineStr">
+        <is>
+          <t>82 Ballymun Road, Glasnevin</t>
+        </is>
+      </c>
+      <c r="H474" s="2" t="inlineStr">
+        <is>
+          <t>D09 PX93</t>
+        </is>
+      </c>
+      <c r="I474" s="2" t="inlineStr">
+        <is>
+          <t>https://thegrapevinedublin.ie</t>
+        </is>
+      </c>
+      <c r="J474" s="2" t="inlineStr"/>
+      <c r="K474" s="2" t="inlineStr"/>
+      <c r="L474" s="2" t="inlineStr"/>
+      <c r="M474" s="2" t="inlineStr"/>
+      <c r="N474" s="2" t="inlineStr">
+        <is>
+          <t>thegrapevineofflicence@gmail.com</t>
+        </is>
+      </c>
+      <c r="O474" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 884 4988</t>
+        </is>
+      </c>
+      <c r="P474" s="2" t="inlineStr"/>
+      <c r="Q474" s="2" t="inlineStr"/>
+      <c r="R474" s="2" t="inlineStr"/>
+      <c r="S474" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TheGrapeVineOffLicence</t>
+        </is>
+      </c>
+      <c r="T474" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thegrapevinedublin</t>
+        </is>
+      </c>
+      <c r="U474" s="2" t="inlineStr"/>
+      <c r="V474" s="2" t="inlineStr"/>
+      <c r="W474" s="2" t="inlineStr"/>
+      <c r="X474" s="2" t="inlineStr"/>
+      <c r="Y474" s="2" t="inlineStr"/>
+      <c r="Z474" s="2" t="inlineStr"/>
+      <c r="AA474" s="2" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>Valeo Foods Ireland</t>
+        </is>
+      </c>
+      <c r="B475" s="2" t="inlineStr">
+        <is>
+          <t>Valeo Foods Ireland</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>7976</t>
+        </is>
+      </c>
+      <c r="D475" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E475" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F475" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G475" s="2" t="inlineStr">
+        <is>
+          <t>79 Broomhill Road, Tallaght</t>
+        </is>
+      </c>
+      <c r="H475" s="2" t="inlineStr">
+        <is>
+          <t>D24 AV9R</t>
+        </is>
+      </c>
+      <c r="I475" s="2" t="inlineStr">
+        <is>
+          <t>https://www.findlaterandco.com</t>
+        </is>
+      </c>
+      <c r="J475" s="2" t="inlineStr"/>
+      <c r="K475" s="2" t="inlineStr"/>
+      <c r="L475" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M475" s="2" t="inlineStr"/>
+      <c r="N475" s="2" t="inlineStr">
+        <is>
+          <t>info@findlaterandco.com</t>
+        </is>
+      </c>
+      <c r="O475" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 404 7300</t>
+        </is>
+      </c>
+      <c r="P475" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q475" s="2" t="inlineStr"/>
+      <c r="R475" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/findlater-co/</t>
+        </is>
+      </c>
+      <c r="S475" s="2" t="inlineStr"/>
+      <c r="T475" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/findlater_and_co</t>
+        </is>
+      </c>
+      <c r="U475" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/FindlaterandCo</t>
+        </is>
+      </c>
+      <c r="V475" s="2" t="inlineStr"/>
+      <c r="W475" s="2" t="inlineStr">
+        <is>
+          <t>Richard Moriarty</t>
+        </is>
+      </c>
+      <c r="X475" s="2" t="inlineStr">
+        <is>
+          <t>Wine &amp; Spirit Director</t>
+        </is>
+      </c>
+      <c r="Y475" s="2" t="inlineStr"/>
+      <c r="Z475" s="2" t="inlineStr"/>
+      <c r="AA475" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rimoriarty/</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>Valeo Foods Ireland</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t>Valeo Foods Ireland</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>7976</t>
+        </is>
+      </c>
+      <c r="D476" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F476" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G476" s="2" t="inlineStr">
+        <is>
+          <t>79 Broomhill Road, Tallaght</t>
+        </is>
+      </c>
+      <c r="H476" s="2" t="inlineStr">
+        <is>
+          <t>D24 AV9R</t>
+        </is>
+      </c>
+      <c r="I476" s="2" t="inlineStr">
+        <is>
+          <t>https://www.findlaterandco.com</t>
+        </is>
+      </c>
+      <c r="J476" s="2" t="inlineStr"/>
+      <c r="K476" s="2" t="inlineStr"/>
+      <c r="L476" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M476" s="2" t="inlineStr"/>
+      <c r="N476" s="2" t="inlineStr">
+        <is>
+          <t>info@findlaterandco.com</t>
+        </is>
+      </c>
+      <c r="O476" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 404 7300</t>
+        </is>
+      </c>
+      <c r="P476" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q476" s="2" t="inlineStr"/>
+      <c r="R476" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/findlater-co/</t>
+        </is>
+      </c>
+      <c r="S476" s="2" t="inlineStr"/>
+      <c r="T476" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/findlater_and_co</t>
+        </is>
+      </c>
+      <c r="U476" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/FindlaterandCo</t>
+        </is>
+      </c>
+      <c r="V476" s="2" t="inlineStr"/>
+      <c r="W476" s="2" t="inlineStr">
+        <is>
+          <t>Declan Bonner</t>
+        </is>
+      </c>
+      <c r="X476" s="2" t="inlineStr">
+        <is>
+          <t>Wine Specialist</t>
+        </is>
+      </c>
+      <c r="Y476" s="2" t="inlineStr"/>
+      <c r="Z476" s="2" t="inlineStr"/>
+      <c r="AA476" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/declan-bonner-8082205b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>Supervalu Ireland</t>
+        </is>
+      </c>
+      <c r="B477" s="2" t="inlineStr">
+        <is>
+          <t>Supervalu Ireland</t>
+        </is>
+      </c>
+      <c r="C477" s="2" t="inlineStr">
+        <is>
+          <t>108273</t>
+        </is>
+      </c>
+      <c r="D477" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E477" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 12</t>
+        </is>
+      </c>
+      <c r="F477" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G477" s="2" t="inlineStr">
+        <is>
+          <t>Walkinstown</t>
+        </is>
+      </c>
+      <c r="H477" s="2" t="inlineStr">
+        <is>
+          <t>D12 XDK2</t>
+        </is>
+      </c>
+      <c r="I477" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.supervalu.ie, https://supervalu.ie</t>
+        </is>
+      </c>
+      <c r="J477" s="2" t="inlineStr"/>
+      <c r="K477" s="2" t="inlineStr"/>
+      <c r="L477" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M477" s="2" t="inlineStr"/>
+      <c r="N477" s="2" t="inlineStr">
+        <is>
+          <t>hannonenfield@supervalu.ie</t>
+        </is>
+      </c>
+      <c r="O477" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 450 5565</t>
+        </is>
+      </c>
+      <c r="P477" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="Q477" s="2" t="inlineStr"/>
+      <c r="R477" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/o-reilly-s-supervalu/</t>
+        </is>
+      </c>
+      <c r="S477" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SuperValuIreland/</t>
+        </is>
+      </c>
+      <c r="T477" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supervalu_irl/</t>
+        </is>
+      </c>
+      <c r="U477" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/supervaluirl</t>
+        </is>
+      </c>
+      <c r="V477" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/SuperValuIreland</t>
+        </is>
+      </c>
+      <c r="W477" s="2" t="inlineStr">
+        <is>
+          <t>Glenn Leacy</t>
+        </is>
+      </c>
+      <c r="X477" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y477" s="2" t="inlineStr"/>
+      <c r="Z477" s="2" t="inlineStr"/>
+      <c r="AA477" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/glenn-leacy-60a89252/</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>Ardkeen Quality Food Store</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>Ardkeen Quality Food Store</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>30284</t>
+        </is>
+      </c>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>Waterford</t>
+        </is>
+      </c>
+      <c r="F478" s="2" t="inlineStr">
+        <is>
+          <t>County Waterford</t>
+        </is>
+      </c>
+      <c r="G478" s="2" t="inlineStr">
+        <is>
+          <t>Dunmore Road</t>
+        </is>
+      </c>
+      <c r="H478" s="2" t="inlineStr">
+        <is>
+          <t>X91 HP9W</t>
+        </is>
+      </c>
+      <c r="I478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ardkeen.com</t>
+        </is>
+      </c>
+      <c r="J478" s="2" t="inlineStr"/>
+      <c r="K478" s="2" t="inlineStr"/>
+      <c r="L478" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M478" s="2" t="inlineStr"/>
+      <c r="N478" s="2" t="inlineStr">
+        <is>
+          <t>info@ardkeen.com</t>
+        </is>
+      </c>
+      <c r="O478" s="2" t="inlineStr">
+        <is>
+          <t>+353 51 874 620</t>
+        </is>
+      </c>
+      <c r="P478" s="2" t="inlineStr">
+        <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="Q478" s="2" t="inlineStr">
+        <is>
+          <t>45413</t>
+        </is>
+      </c>
+      <c r="R478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ardkeen-quality-food-store/</t>
+        </is>
+      </c>
+      <c r="S478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ardkeenqualityfoodstore</t>
+        </is>
+      </c>
+      <c r="T478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ardkeenqualityfoodstore</t>
+        </is>
+      </c>
+      <c r="U478" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/ardkeenqfs</t>
+        </is>
+      </c>
+      <c r="V478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCq9cEZCM7NAwDflY_yJHT5Q</t>
+        </is>
+      </c>
+      <c r="W478" s="2" t="inlineStr">
+        <is>
+          <t>Christine Fowler</t>
+        </is>
+      </c>
+      <c r="X478" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y478" s="2" t="inlineStr"/>
+      <c r="Z478" s="2" t="inlineStr"/>
+      <c r="AA478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cfowler1</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>Bubble Brothers Limited</t>
+        </is>
+      </c>
+      <c r="B479" s="2" t="inlineStr">
+        <is>
+          <t>Bubble Brothers Limited</t>
+        </is>
+      </c>
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>26091</t>
+        </is>
+      </c>
+      <c r="D479" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E479" s="2" t="inlineStr">
+        <is>
+          <t>Cork</t>
+        </is>
+      </c>
+      <c r="F479" s="2" t="inlineStr">
+        <is>
+          <t>County Cork</t>
+        </is>
+      </c>
+      <c r="G479" s="2" t="inlineStr">
+        <is>
+          <t>Marina Commercial Park, Centre Park Road</t>
+        </is>
+      </c>
+      <c r="H479" s="2" t="inlineStr">
+        <is>
+          <t>T12 ND2W</t>
+        </is>
+      </c>
+      <c r="I479" s="2" t="inlineStr">
+        <is>
+          <t>http://www.marypawlewines.com, https://bubblebrothers.ie</t>
+        </is>
+      </c>
+      <c r="J479" s="2" t="inlineStr"/>
+      <c r="K479" s="2" t="inlineStr"/>
+      <c r="L479" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M479" s="2" t="inlineStr"/>
+      <c r="N479" s="2" t="inlineStr">
+        <is>
+          <t>info@bubblebrothers.ie</t>
+        </is>
+      </c>
+      <c r="O479" s="2" t="inlineStr">
+        <is>
+          <t>+353 21 431 6000</t>
+        </is>
+      </c>
+      <c r="P479" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q479" s="2" t="inlineStr">
+        <is>
+          <t>291250</t>
+        </is>
+      </c>
+      <c r="R479" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bubble-brothers</t>
+        </is>
+      </c>
+      <c r="S479" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bubblebrothers</t>
+        </is>
+      </c>
+      <c r="T479" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bubblebrotherscork/</t>
+        </is>
+      </c>
+      <c r="U479" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/bubblebrothers</t>
+        </is>
+      </c>
+      <c r="V479" s="2" t="inlineStr"/>
+      <c r="W479" s="2" t="inlineStr">
+        <is>
+          <t>Billy Forrester</t>
+        </is>
+      </c>
+      <c r="X479" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y479" s="2" t="inlineStr"/>
+      <c r="Z479" s="2" t="inlineStr"/>
+      <c r="AA479" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/billy-forrester-a5697b36/</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>Jj Mahons &amp; Sons</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>Jj Mahons &amp; Sons</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>20930</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="inlineStr">
+        <is>
+          <t>Kildare</t>
+        </is>
+      </c>
+      <c r="F480" s="2" t="inlineStr">
+        <is>
+          <t>County Kildare</t>
+        </is>
+      </c>
+      <c r="G480" s="2" t="inlineStr">
+        <is>
+          <t>Cross Keys</t>
+        </is>
+      </c>
+      <c r="H480" s="2" t="inlineStr">
+        <is>
+          <t>R51 C625</t>
+        </is>
+      </c>
+      <c r="I480" s="2" t="inlineStr">
+        <is>
+          <t>http://jjmahons.com</t>
+        </is>
+      </c>
+      <c r="J480" s="2" t="inlineStr"/>
+      <c r="K480" s="2" t="inlineStr"/>
+      <c r="L480" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M480" s="2" t="inlineStr"/>
+      <c r="N480" s="2" t="inlineStr">
+        <is>
+          <t>info@jjmahons.com</t>
+        </is>
+      </c>
+      <c r="O480" s="2" t="inlineStr">
+        <is>
+          <t>+353 45 521 316</t>
+        </is>
+      </c>
+      <c r="P480" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="Q480" s="2" t="inlineStr">
+        <is>
+          <t>32542</t>
+        </is>
+      </c>
+      <c r="R480" s="2" t="inlineStr"/>
+      <c r="S480" s="2" t="inlineStr"/>
+      <c r="T480" s="2" t="inlineStr"/>
+      <c r="U480" s="2" t="inlineStr"/>
+      <c r="V480" s="2" t="inlineStr"/>
+      <c r="W480" s="2" t="inlineStr">
+        <is>
+          <t>David Mahon</t>
+        </is>
+      </c>
+      <c r="X480" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y480" s="2" t="inlineStr"/>
+      <c r="Z480" s="2" t="inlineStr"/>
+      <c r="AA480" s="2" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>Jj Mahons &amp; Sons</t>
+        </is>
+      </c>
+      <c r="B481" s="2" t="inlineStr">
+        <is>
+          <t>Jj Mahons &amp; Sons</t>
+        </is>
+      </c>
+      <c r="C481" s="2" t="inlineStr">
+        <is>
+          <t>20930</t>
+        </is>
+      </c>
+      <c r="D481" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E481" s="2" t="inlineStr">
+        <is>
+          <t>Kildare</t>
+        </is>
+      </c>
+      <c r="F481" s="2" t="inlineStr">
+        <is>
+          <t>County Kildare</t>
+        </is>
+      </c>
+      <c r="G481" s="2" t="inlineStr">
+        <is>
+          <t>Cross Keys</t>
+        </is>
+      </c>
+      <c r="H481" s="2" t="inlineStr">
+        <is>
+          <t>R51 C625</t>
+        </is>
+      </c>
+      <c r="I481" s="2" t="inlineStr">
+        <is>
+          <t>http://jjmahons.com</t>
+        </is>
+      </c>
+      <c r="J481" s="2" t="inlineStr"/>
+      <c r="K481" s="2" t="inlineStr"/>
+      <c r="L481" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M481" s="2" t="inlineStr"/>
+      <c r="N481" s="2" t="inlineStr">
+        <is>
+          <t>info@jjmahons.com</t>
+        </is>
+      </c>
+      <c r="O481" s="2" t="inlineStr">
+        <is>
+          <t>+353 45 521 316</t>
+        </is>
+      </c>
+      <c r="P481" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="Q481" s="2" t="inlineStr">
+        <is>
+          <t>32542</t>
+        </is>
+      </c>
+      <c r="R481" s="2" t="inlineStr"/>
+      <c r="S481" s="2" t="inlineStr"/>
+      <c r="T481" s="2" t="inlineStr"/>
+      <c r="U481" s="2" t="inlineStr"/>
+      <c r="V481" s="2" t="inlineStr"/>
+      <c r="W481" s="2" t="inlineStr">
+        <is>
+          <t>Julie McMahon</t>
+        </is>
+      </c>
+      <c r="X481" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y481" s="2" t="inlineStr"/>
+      <c r="Z481" s="2" t="inlineStr"/>
+      <c r="AA481" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/julie-mcmahon-2595ab35/</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>Copsewood Limited</t>
+        </is>
+      </c>
+      <c r="B482" s="2" t="inlineStr">
+        <is>
+          <t>Copsewood Limited</t>
+        </is>
+      </c>
+      <c r="C482" s="2" t="inlineStr">
+        <is>
+          <t>8051</t>
+        </is>
+      </c>
+      <c r="D482" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E482" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F482" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G482" s="2" t="inlineStr">
+        <is>
+          <t>Portmarnock Town Centre,  Strand Road, Portmarnock</t>
+        </is>
+      </c>
+      <c r="H482" s="2" t="inlineStr">
+        <is>
+          <t>D13 FP28</t>
+        </is>
+      </c>
+      <c r="I482" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jusdevine.ie</t>
+        </is>
+      </c>
+      <c r="J482" s="2" t="inlineStr"/>
+      <c r="K482" s="2" t="inlineStr"/>
+      <c r="L482" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M482" s="2" t="inlineStr"/>
+      <c r="N482" s="2" t="inlineStr">
+        <is>
+          <t>info@jusdevine.ie</t>
+        </is>
+      </c>
+      <c r="O482" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 846 1192</t>
+        </is>
+      </c>
+      <c r="P482" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q482" s="2" t="inlineStr">
+        <is>
+          <t>167088</t>
+        </is>
+      </c>
+      <c r="R482" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jus-de-vine-wine-shop/</t>
+        </is>
+      </c>
+      <c r="S482" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/jusdevineportmarnock/</t>
+        </is>
+      </c>
+      <c r="T482" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jusdevine_/</t>
+        </is>
+      </c>
+      <c r="U482" s="2" t="inlineStr"/>
+      <c r="V482" s="2" t="inlineStr"/>
+      <c r="W482" s="2" t="inlineStr"/>
+      <c r="X482" s="2" t="inlineStr"/>
+      <c r="Y482" s="2" t="inlineStr"/>
+      <c r="Z482" s="2" t="inlineStr"/>
+      <c r="AA482" s="2" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="inlineStr">
+        <is>
+          <t>O'donovans Off Licence Limited</t>
+        </is>
+      </c>
+      <c r="B483" s="2" t="inlineStr">
+        <is>
+          <t>O'donovans Off Licence Limited</t>
+        </is>
+      </c>
+      <c r="C483" s="2" t="inlineStr">
+        <is>
+          <t>8071</t>
+        </is>
+      </c>
+      <c r="D483" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E483" s="2" t="inlineStr">
+        <is>
+          <t>Cork</t>
+        </is>
+      </c>
+      <c r="F483" s="2" t="inlineStr">
+        <is>
+          <t>Co. Cork</t>
+        </is>
+      </c>
+      <c r="G483" s="2" t="inlineStr">
+        <is>
+          <t>Cork Bonded Warehouse, Little Island Business Park, Little Island</t>
+        </is>
+      </c>
+      <c r="H483" s="2" t="inlineStr">
+        <is>
+          <t>T45 VY26</t>
+        </is>
+      </c>
+      <c r="I483" s="2" t="inlineStr">
+        <is>
+          <t>https://www.odonovansofflicence.com</t>
+        </is>
+      </c>
+      <c r="J483" s="2" t="inlineStr"/>
+      <c r="K483" s="2" t="inlineStr"/>
+      <c r="L483" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M483" s="2" t="inlineStr"/>
+      <c r="N483" s="2" t="inlineStr">
+        <is>
+          <t>info@odonovansofflicence.com</t>
+        </is>
+      </c>
+      <c r="O483" s="2" t="inlineStr">
+        <is>
+          <t>+353 21 429 6060</t>
+        </is>
+      </c>
+      <c r="P483" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q483" s="2" t="inlineStr">
+        <is>
+          <t>331387</t>
+        </is>
+      </c>
+      <c r="R483" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/o'donovans-off-licence</t>
+        </is>
+      </c>
+      <c r="S483" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/odonovansofflicences</t>
+        </is>
+      </c>
+      <c r="T483" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/odonovansofflicence</t>
+        </is>
+      </c>
+      <c r="U483" s="2" t="inlineStr"/>
+      <c r="V483" s="2" t="inlineStr"/>
+      <c r="W483" s="2" t="inlineStr">
+        <is>
+          <t>Gary O'Donovan</t>
+        </is>
+      </c>
+      <c r="X483" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y483" s="2" t="inlineStr"/>
+      <c r="Z483" s="2" t="inlineStr"/>
+      <c r="AA483" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gary-o-donovan-ba-wset-dip-59a92616/</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>Tankersley Wine Brokers Limited</t>
+        </is>
+      </c>
+      <c r="B484" s="2" t="inlineStr">
+        <is>
+          <t>Tankersley Wine Brokers Limited</t>
+        </is>
+      </c>
+      <c r="C484" s="2" t="inlineStr">
+        <is>
+          <t>8023</t>
+        </is>
+      </c>
+      <c r="D484" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="inlineStr">
+        <is>
+          <t>Tinahely</t>
+        </is>
+      </c>
+      <c r="F484" s="2" t="inlineStr">
+        <is>
+          <t>Co. Wicklow</t>
+        </is>
+      </c>
+      <c r="G484" s="2" t="inlineStr">
+        <is>
+          <t>Tankersley Cottage, Preban</t>
+        </is>
+      </c>
+      <c r="H484" s="2" t="inlineStr">
+        <is>
+          <t>Y14 YV09</t>
+        </is>
+      </c>
+      <c r="I484" s="2" t="inlineStr">
+        <is>
+          <t>https://tankersleywine.com</t>
+        </is>
+      </c>
+      <c r="J484" s="2" t="inlineStr"/>
+      <c r="K484" s="2" t="inlineStr"/>
+      <c r="L484" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M484" s="2" t="inlineStr"/>
+      <c r="N484" s="2" t="inlineStr">
+        <is>
+          <t>info@tankersleywine.ie</t>
+        </is>
+      </c>
+      <c r="O484" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 485 2694</t>
+        </is>
+      </c>
+      <c r="P484" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q484" s="2" t="inlineStr">
+        <is>
+          <t>329628</t>
+        </is>
+      </c>
+      <c r="R484" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tankersley-wine-brokers/</t>
+        </is>
+      </c>
+      <c r="S484" s="2" t="inlineStr"/>
+      <c r="T484" s="2" t="inlineStr"/>
+      <c r="U484" s="2" t="inlineStr"/>
+      <c r="V484" s="2" t="inlineStr"/>
+      <c r="W484" s="2" t="inlineStr"/>
+      <c r="X484" s="2" t="inlineStr"/>
+      <c r="Y484" s="2" t="inlineStr"/>
+      <c r="Z484" s="2" t="inlineStr"/>
+      <c r="AA484" s="2" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>J.j. Fox Limited</t>
+        </is>
+      </c>
+      <c r="B485" s="2" t="inlineStr">
+        <is>
+          <t>J.j. Fox Limited</t>
+        </is>
+      </c>
+      <c r="C485" s="2" t="inlineStr">
+        <is>
+          <t>28785</t>
+        </is>
+      </c>
+      <c r="D485" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E485" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F485" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G485" s="2" t="inlineStr">
+        <is>
+          <t>119 Grafton Street</t>
+        </is>
+      </c>
+      <c r="H485" s="2" t="inlineStr">
+        <is>
+          <t>D02 E620</t>
+        </is>
+      </c>
+      <c r="I485" s="2" t="inlineStr">
+        <is>
+          <t>https://jamesfox.ie</t>
+        </is>
+      </c>
+      <c r="J485" s="2" t="inlineStr"/>
+      <c r="K485" s="2" t="inlineStr"/>
+      <c r="L485" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M485" s="2" t="inlineStr"/>
+      <c r="N485" s="2" t="inlineStr">
+        <is>
+          <t>info@jamesfox.ie</t>
+        </is>
+      </c>
+      <c r="O485" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 677 0533</t>
+        </is>
+      </c>
+      <c r="P485" s="2" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="Q485" s="2" t="inlineStr">
+        <is>
+          <t>9864</t>
+        </is>
+      </c>
+      <c r="R485" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/james-fox-cigar-&amp;-whiskey-store</t>
+        </is>
+      </c>
+      <c r="S485" s="2" t="inlineStr"/>
+      <c r="T485" s="2" t="inlineStr"/>
+      <c r="U485" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/jamesfoxdublin</t>
+        </is>
+      </c>
+      <c r="V485" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/JamesJFoxDublin</t>
+        </is>
+      </c>
+      <c r="W485" s="2" t="inlineStr">
+        <is>
+          <t>Yiorgos Manesis</t>
+        </is>
+      </c>
+      <c r="X485" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y485" s="2" t="inlineStr"/>
+      <c r="Z485" s="2" t="inlineStr"/>
+      <c r="AA485" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/yiorgosmanesis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>J.j. Fox Limited</t>
+        </is>
+      </c>
+      <c r="B486" s="2" t="inlineStr">
+        <is>
+          <t>J.j. Fox Limited</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="inlineStr">
+        <is>
+          <t>28785</t>
+        </is>
+      </c>
+      <c r="D486" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E486" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F486" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G486" s="2" t="inlineStr">
+        <is>
+          <t>119 Grafton Street</t>
+        </is>
+      </c>
+      <c r="H486" s="2" t="inlineStr">
+        <is>
+          <t>D02 E620</t>
+        </is>
+      </c>
+      <c r="I486" s="2" t="inlineStr">
+        <is>
+          <t>https://jamesfox.ie</t>
+        </is>
+      </c>
+      <c r="J486" s="2" t="inlineStr"/>
+      <c r="K486" s="2" t="inlineStr"/>
+      <c r="L486" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M486" s="2" t="inlineStr"/>
+      <c r="N486" s="2" t="inlineStr">
+        <is>
+          <t>info@jamesfox.ie</t>
+        </is>
+      </c>
+      <c r="O486" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 677 0533</t>
+        </is>
+      </c>
+      <c r="P486" s="2" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="Q486" s="2" t="inlineStr">
+        <is>
+          <t>9864</t>
+        </is>
+      </c>
+      <c r="R486" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/james-fox-cigar-&amp;-whiskey-store</t>
+        </is>
+      </c>
+      <c r="S486" s="2" t="inlineStr"/>
+      <c r="T486" s="2" t="inlineStr"/>
+      <c r="U486" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/jamesfoxdublin</t>
+        </is>
+      </c>
+      <c r="V486" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/JamesJFoxDublin</t>
+        </is>
+      </c>
+      <c r="W486" s="2" t="inlineStr">
+        <is>
+          <t>Amy Catherine</t>
+        </is>
+      </c>
+      <c r="X486" s="2" t="inlineStr">
+        <is>
+          <t>Sales Executive</t>
+        </is>
+      </c>
+      <c r="Y486" s="2" t="inlineStr"/>
+      <c r="Z486" s="2" t="inlineStr"/>
+      <c r="AA486" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/amy-catherine-mcloughlin-4246a819a/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
